--- a/artfynd/A 14449-2024 artfynd.xlsx
+++ b/artfynd/A 14449-2024 artfynd.xlsx
@@ -2189,7 +2189,7 @@
         <v>121917049</v>
       </c>
       <c r="B16" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
